--- a/WFiles/simulation_results_wind_backramp2.xlsx
+++ b/WFiles/simulation_results_wind_backramp2.xlsx
@@ -425,230 +425,270 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>BackwardRamp2_bucket</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Darwin_net_pnl_x</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Fourier_net_pnl_x</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Darwin_net_pnl_y</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Darwin_slack_pnl</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Darwin_cong_pnl</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Fourier_net_pnl_y</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Fourier_slack_pnl</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Fourier_cong_pnl</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>(-3675.662, -2615.924]</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>-2357</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>535</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>37378</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>36047</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>1160</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>15053</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>9372</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>5507</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>(-2615.924, -1563.552]</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>-10787</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="n">
         <v>-11360</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>-1230</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>-7721</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>7356</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>-53723</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>-69781</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>16317</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>(-1563.552, -511.181]</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>30910</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="n">
         <v>57898</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>-203810</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>-406541</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>185549</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>-341426</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>-624602</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>269158</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>(-511.181, 541.191]</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>46059</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="n">
         <v>50530</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>630668</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>265284</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>369512</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>-170026</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>-430057</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>269031</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>(541.191, 1593.562]</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>16887</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" t="n">
         <v>52134</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>-12566</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>-170125</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>152628</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>-121760</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>-248382</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>126670</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>(1593.562, 2645.934]</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>-3685</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
         <v>15927</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>99799</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>17336</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>81149</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>-18249</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>-71008</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>51255</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>(2645.934, 3698.305]</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>-4332</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" t="n">
         <v>3358</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>973</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>-67428</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>68345</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>-11799</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>-51471</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>39854</v>
       </c>
     </row>
